--- a/datos/fomrato nuevo api jaboneria/EJEMPLO_AcuerdoCompleto_Distribuidor.xlsx
+++ b/datos/fomrato nuevo api jaboneria/EJEMPLO_AcuerdoCompleto_Distribuidor.xlsx
@@ -1,55 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\fomrato nuevo api jaboneria\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1F7B5C-8D18-49E3-B457-79E36257133A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACUERDO COMPLETO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ACUERDO COMPLETO" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+  <si>
+    <t>META DE COMPRAS</t>
+  </si>
+  <si>
+    <t>CABECERA</t>
+  </si>
+  <si>
+    <t>RUMA</t>
+  </si>
+  <si>
+    <t>PERCHA</t>
+  </si>
+  <si>
+    <t>USUARIO</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDOR</t>
+  </si>
+  <si>
+    <t>CIUDAD</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>CODIGO</t>
+  </si>
+  <si>
+    <t>RUC</t>
+  </si>
+  <si>
+    <t>CATEGORIA</t>
+  </si>
+  <si>
+    <t>SUBCATEGORIA</t>
+  </si>
+  <si>
+    <t>MARCA</t>
+  </si>
+  <si>
+    <t>ENERO</t>
+  </si>
+  <si>
+    <t>FEBRERO</t>
+  </si>
+  <si>
+    <t>MARZO</t>
+  </si>
+  <si>
+    <t>CANTIDAD</t>
+  </si>
+  <si>
+    <t>PRODISPRO CIA LTDA</t>
+  </si>
+  <si>
+    <t>IBARRA</t>
+  </si>
+  <si>
+    <t>INTYS MARKET SOCIEDAD CIVIL COMERCIAL</t>
+  </si>
+  <si>
+    <t>CREMA</t>
+  </si>
+  <si>
+    <t>LAVAVAJILLAS</t>
+  </si>
+  <si>
+    <t>LAVA</t>
+  </si>
+  <si>
+    <t>BARRA</t>
+  </si>
+  <si>
+    <t>ROPA</t>
+  </si>
+  <si>
+    <t>EL MACHO</t>
+  </si>
+  <si>
+    <t>Diego Constante</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000288E"/>
-        <bgColor rgb="0000288E"/>
+        <fgColor rgb="FF00288E"/>
+        <bgColor rgb="FF00288E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C0E6F5"/>
-        <bgColor rgb="00C0E6F5"/>
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,83 +164,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -429,269 +470,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" customWidth="1"/>
+    <col min="4" max="4" width="36.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="15" max="18" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>META DE COMPRAS</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>CABECERA</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>RUMA</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>PERCHA</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="J1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>USUARIO</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>DISTRIBUIDOR</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>CIUDAD</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>NOMBRE</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>CODIGO</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>RUC</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>CATEGORIA</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>SUBCATEGORIA</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>MARCA</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>ENERO</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>FEBRERO</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>ENERO</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>FEBRERO</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>MARZO</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>RUMA</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>CANTIDAD</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>ENERO</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>FEBRERO</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>MARZO</t>
-        </is>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PRODISPRO CIA LTDA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>IBARRA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>INTYS MARKET SOCIEDAD CIVIL COMERCIAL</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>CREMA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>LAVAVAJILLAS</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>LAVA</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3">
         <v>180</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3">
         <v>180</v>
       </c>
-      <c r="L3" t="n">
-        <v>180</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>60</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>60</v>
       </c>
-      <c r="O3" t="n">
-        <v>60</v>
-      </c>
-      <c r="P3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="O3">
+        <v>10</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3">
         <v>50</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3">
         <v>50</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3">
         <v>50</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PRODISPRO CIA LTDA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>IBARRA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>INTYS MARKET SOCIEDAD CIVIL COMERCIAL</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BARRA</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>ROPA</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>EL MACHO</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4">
         <v>9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>9</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>9</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
